--- a/docs/doc/magpi/SourcingMagPi.xlsx
+++ b/docs/doc/magpi/SourcingMagPi.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ofauvarq\Documents\GitHub\DocumentationsKOSMOS\MagpiSystem\sourcing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ofauvarq\Documents\GitHub\KOSMOS\docs\doc\magpi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDE73E1-0D47-4D9F-BD6F-3A79FF53F612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F179D8E6-D4BB-4A2A-AD4A-5CB06C052053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-4872" windowWidth="30936" windowHeight="16896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste_Materiel" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="126">
   <si>
     <t>Dernière mise à jour :</t>
   </si>
@@ -237,27 +237,9 @@
     <t>https://www.amazon.fr/Neulriscn-R%C3%A9glable-Batteries-Dimpulsion-Fabrication/dp/B0DNQHWD2Q/ref=sr_1_1?__mk_fr_FR=%C3%85M%C3%85%C5%BD%C3%95%C3%91&amp;s=hi&amp;sr=1-1</t>
   </si>
   <si>
-    <t>DIGIKEY</t>
-  </si>
-  <si>
-    <t>Digikey</t>
-  </si>
-  <si>
     <t>Carte micro SD 256 GB</t>
   </si>
   <si>
-    <t>Sahasra Electronic Solutions Limited CA227-011</t>
-  </si>
-  <si>
-    <t>5093-CA227-011-ND</t>
-  </si>
-  <si>
-    <t>https://www.digikey.fr/fr/products/detail/sahasra-electronic-solutions-limited/CA227-011/22532602</t>
-  </si>
-  <si>
-    <t>https://www.gotronic.fr/art-carte-raspberry-pi-5-8-gb-38177.htm</t>
-  </si>
-  <si>
     <t>https://www.gotronic.fr/art-batterie-rtc-pour-raspberry-pi-5-38451.htm</t>
   </si>
   <si>
@@ -415,6 +397,24 @@
   </si>
   <si>
     <t>Vis caméra (solution 1 &amp; 1bis)</t>
+  </si>
+  <si>
+    <t>https://www.gotronic.fr/art-carte-raspberry-pi-5-2-gb-39733.htm</t>
+  </si>
+  <si>
+    <t>38912</t>
+  </si>
+  <si>
+    <t>RS</t>
+  </si>
+  <si>
+    <t>Micro SD 256 Go PLAY microSDXC UHS-I Card Lexar MicroSDXC UHS-I, A1, Classe 10</t>
+  </si>
+  <si>
+    <t>254-2664</t>
+  </si>
+  <si>
+    <t>https://fr.rs-online.com/web/p/cartes-sd/2542664?gb=a</t>
   </si>
 </sst>
 </file>
@@ -752,7 +752,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -908,6 +908,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="29">
@@ -1163,7 +1166,7 @@
       </c>
       <c r="B1" s="9">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46293</v>
       </c>
       <c r="C1" s="57"/>
       <c r="D1" s="57"/>
@@ -1232,7 +1235,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>9</v>
@@ -1240,24 +1243,24 @@
       <c r="D5" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="55">
-        <v>38580</v>
+      <c r="E5" s="55" t="s">
+        <v>121</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="G5" s="21">
         <v>1</v>
       </c>
       <c r="H5" s="22">
-        <v>95.75</v>
+        <v>69.67</v>
       </c>
       <c r="I5" s="22">
-        <v>114.9</v>
+        <v>86.6</v>
       </c>
       <c r="J5" s="22">
         <f>G5*I5</f>
-        <v>114.9</v>
+        <v>86.6</v>
       </c>
       <c r="XEZ5" s="7"/>
       <c r="XFA5" s="6"/>
@@ -1268,7 +1271,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C6" s="23" t="s">
         <v>10</v>
@@ -1280,7 +1283,7 @@
         <v>38644</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G6" s="21">
         <v>1</v>
@@ -1304,7 +1307,7 @@
         <v>18</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>12</v>
@@ -1316,7 +1319,7 @@
         <v>11937</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G7" s="21">
         <v>1</v>
@@ -1343,16 +1346,16 @@
         <v>51</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E8" s="56" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G8" s="28">
         <v>0</v>
@@ -1377,29 +1380,29 @@
         <v>51</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E9" s="56" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G9" s="28">
         <v>1</v>
       </c>
       <c r="H9" s="29">
-        <v>62.42</v>
+        <v>58.25</v>
       </c>
       <c r="I9" s="29">
-        <v>74.900000000000006</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="J9" s="22">
         <f t="shared" si="0"/>
-        <v>74.900000000000006</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="XFB9" s="7"/>
     </row>
@@ -1411,16 +1414,16 @@
         <v>51</v>
       </c>
       <c r="C10" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="E10" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" s="39" t="s">
         <v>115</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="E10" s="56" t="s">
-        <v>122</v>
-      </c>
-      <c r="F10" s="39" t="s">
-        <v>121</v>
       </c>
       <c r="G10" s="28">
         <v>0</v>
@@ -1454,20 +1457,20 @@
         <v>59</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G11" s="21">
         <v>1</v>
       </c>
       <c r="H11" s="22">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="I11" s="22">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J11" s="22">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="XEZ11" s="7"/>
       <c r="XFA11" s="6"/>
@@ -1486,11 +1489,11 @@
       <c r="D12" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="55">
+      <c r="E12" s="58">
         <v>11356</v>
       </c>
-      <c r="F12" s="18" t="s">
-        <v>76</v>
+      <c r="F12" s="39" t="s">
+        <v>70</v>
       </c>
       <c r="G12" s="21">
         <v>1</v>
@@ -1522,10 +1525,10 @@
       <c r="D13" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="55">
+      <c r="E13" s="58">
         <v>48918</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="39" t="s">
         <v>43</v>
       </c>
       <c r="G13" s="21">
@@ -1550,19 +1553,19 @@
         <v>18</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="E14" s="55" t="s">
-        <v>83</v>
+        <v>76</v>
+      </c>
+      <c r="E14" s="58" t="s">
+        <v>77</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G14" s="21">
         <v>1</v>
@@ -1586,19 +1589,19 @@
         <v>18</v>
       </c>
       <c r="B15" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="E15" s="55" t="s">
-        <v>88</v>
+      <c r="E15" s="58" t="s">
+        <v>82</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G15" s="21">
         <v>1</v>
@@ -1622,19 +1625,19 @@
         <v>18</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E16" s="55" t="s">
-        <v>91</v>
+        <v>84</v>
+      </c>
+      <c r="E16" s="58" t="s">
+        <v>85</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G16" s="21">
         <v>1</v>
@@ -1658,19 +1661,19 @@
         <v>18</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="E17" s="55" t="s">
-        <v>97</v>
+        <v>88</v>
+      </c>
+      <c r="E17" s="58" t="s">
+        <v>91</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G17" s="21">
         <v>1</v>
@@ -1694,19 +1697,19 @@
         <v>18</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" s="55" t="s">
-        <v>100</v>
+        <v>92</v>
+      </c>
+      <c r="E18" s="58" t="s">
+        <v>94</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G18" s="21">
         <v>1</v>
@@ -1730,19 +1733,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="E19" s="55" t="s">
-        <v>103</v>
+        <v>95</v>
+      </c>
+      <c r="E19" s="58" t="s">
+        <v>97</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G19" s="21">
         <v>1</v>
@@ -1807,13 +1810,13 @@
         <v>57</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D22" s="18" t="s">
         <v>15</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F22" s="39" t="s">
         <v>17</v>
@@ -1856,7 +1859,7 @@
     </row>
     <row r="24" spans="1:10 16377:16382" s="4" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="47" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="23"/>
@@ -1879,35 +1882,35 @@
     </row>
     <row r="25" spans="1:10 16377:16382" s="4" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="F25" s="39" t="s">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="G25" s="21">
         <v>1</v>
       </c>
       <c r="H25" s="31">
-        <v>67.790000000000006</v>
+        <v>64.040000000000006</v>
       </c>
       <c r="I25" s="22">
-        <v>81.34</v>
+        <v>76.849999999999994</v>
       </c>
       <c r="J25" s="22">
         <f t="shared" si="0"/>
-        <v>81.34</v>
+        <v>76.849999999999994</v>
       </c>
       <c r="XEW25" s="6"/>
       <c r="XEX25" s="6"/>
@@ -1968,11 +1971,11 @@
         <v>22</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E28" s="19"/>
       <c r="F28" s="39" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G28" s="21">
         <v>1</v>
@@ -2157,14 +2160,14 @@
         <v>14</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E34" s="19"/>
       <c r="F34" s="39" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G34" s="21">
         <v>1</v>
@@ -2186,17 +2189,17 @@
         <v>19</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E35" s="19"/>
       <c r="F35" s="39" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G35" s="21">
         <v>1</v>
@@ -2702,20 +2705,20 @@
     <hyperlink ref="F32" r:id="rId9" xr:uid="{44404973-6C89-4028-938B-E5D90DCBE423}"/>
     <hyperlink ref="F33" r:id="rId10" xr:uid="{116D8E0B-3140-4844-85AB-D40FCE69618E}"/>
     <hyperlink ref="F34" r:id="rId11" xr:uid="{DB12AF66-C776-49E9-89BA-BF9EF34FDC02}"/>
-    <hyperlink ref="F25" r:id="rId12" xr:uid="{82629390-AC3E-4A68-8ECF-BE8FDB39D43D}"/>
-    <hyperlink ref="F5" r:id="rId13" xr:uid="{06046FFE-A198-4842-A3A9-F2336B8D2333}"/>
-    <hyperlink ref="F6" r:id="rId14" xr:uid="{9CB6AAC2-5586-4E44-94B1-FA3F89ADDB3D}"/>
-    <hyperlink ref="F7" r:id="rId15" xr:uid="{5A14520F-F507-480E-ADD0-FAC9DE84725D}"/>
-    <hyperlink ref="F8" r:id="rId16" xr:uid="{7B85981C-F9AB-454A-B211-1AAC3F35C0B7}"/>
-    <hyperlink ref="F11" r:id="rId17" xr:uid="{D91272D4-4E75-44C5-89EB-8ECB9EBC8B1D}"/>
-    <hyperlink ref="F14" r:id="rId18" xr:uid="{CC541A1A-C9A4-4570-8E4D-DD6E429ACE15}"/>
-    <hyperlink ref="F15" r:id="rId19" xr:uid="{7628B59D-8DB8-41FD-904D-8ED75673F6EF}"/>
-    <hyperlink ref="F16" r:id="rId20" xr:uid="{0B9BEE83-5B73-4D6D-B6A1-885D5D495E64}"/>
-    <hyperlink ref="F17" r:id="rId21" xr:uid="{68FCA54B-4433-4DC8-8BE0-08B3D901E5B4}"/>
-    <hyperlink ref="F19" r:id="rId22" xr:uid="{51A1F655-D4DB-4FBD-B02E-DD25A8F08C96}"/>
-    <hyperlink ref="F35" r:id="rId23" xr:uid="{A0E09CA1-1E52-48B6-8070-5DFA96766280}"/>
+    <hyperlink ref="F5" r:id="rId12" xr:uid="{06046FFE-A198-4842-A3A9-F2336B8D2333}"/>
+    <hyperlink ref="F6" r:id="rId13" xr:uid="{9CB6AAC2-5586-4E44-94B1-FA3F89ADDB3D}"/>
+    <hyperlink ref="F7" r:id="rId14" xr:uid="{5A14520F-F507-480E-ADD0-FAC9DE84725D}"/>
+    <hyperlink ref="F8" r:id="rId15" xr:uid="{7B85981C-F9AB-454A-B211-1AAC3F35C0B7}"/>
+    <hyperlink ref="F11" r:id="rId16" xr:uid="{D91272D4-4E75-44C5-89EB-8ECB9EBC8B1D}"/>
+    <hyperlink ref="F14" r:id="rId17" xr:uid="{CC541A1A-C9A4-4570-8E4D-DD6E429ACE15}"/>
+    <hyperlink ref="F15" r:id="rId18" xr:uid="{7628B59D-8DB8-41FD-904D-8ED75673F6EF}"/>
+    <hyperlink ref="F16" r:id="rId19" xr:uid="{0B9BEE83-5B73-4D6D-B6A1-885D5D495E64}"/>
+    <hyperlink ref="F17" r:id="rId20" xr:uid="{68FCA54B-4433-4DC8-8BE0-08B3D901E5B4}"/>
+    <hyperlink ref="F19" r:id="rId21" xr:uid="{51A1F655-D4DB-4FBD-B02E-DD25A8F08C96}"/>
+    <hyperlink ref="F35" r:id="rId22" xr:uid="{A0E09CA1-1E52-48B6-8070-5DFA96766280}"/>
+    <hyperlink ref="F10" r:id="rId23" xr:uid="{E7F9CC3A-1C68-4385-A8EE-68D678C64344}"/>
     <hyperlink ref="F9" r:id="rId24" xr:uid="{B47A695C-7DD6-48A0-A49A-D555C141796D}"/>
-    <hyperlink ref="F10" r:id="rId25" xr:uid="{E7F9CC3A-1C68-4385-A8EE-68D678C64344}"/>
+    <hyperlink ref="F12" r:id="rId25" xr:uid="{1CD51444-1335-4FB2-93F3-C14F69CA9FAD}"/>
   </hyperlinks>
   <pageMargins left="0.62361111111111101" right="0.58055555555555605" top="0.48958333333333298" bottom="0.57430555555555596" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="8" scale="42" fitToWidth="0" pageOrder="overThenDown" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId26"/>
